--- a/examples/excel/charts/charts-pie.xlsx
+++ b/examples/excel/charts/charts-pie.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Pie Charts" sheetId="2" r:id="R315ae2af4aa64501"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Doughnut Charts" sheetId="3" r:id="R1b26189e651545c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Pie Charts" sheetId="2" r:id="Re9466078d28e4559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Doughnut Charts" sheetId="3" r:id="R3f4ca487b35248b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Pie Advanced" sheetId="4" r:id="Re87516badd5445d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -99,7 +100,6 @@
           </c:val>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -107,6 +107,349 @@
           <c:showPercent val="0"/>
         </c:dLbls>
       </c:pieChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Doughnut — holeSize + leaderlines</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Revenue</c:v>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>North</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>South</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>East</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>West</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>28</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>22</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>15</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:holeSize val="65"/>
+      </c:doughnutChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Overlaid Title</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Mix</c:v>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>Online</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Retail</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Partner</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>20</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+        </c:dLbls>
+      </c:pieChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Doughnut — Combined</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Split</c:v>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>C</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>20</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1200" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+        </c:dLbls>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -149,6 +492,7 @@
           <c:tx>
             <c:v>Revenue</c:v>
           </c:tx>
+          <c:explosion val="15"/>
           <c:cat>
             <c:strLit>
               <c:ptCount val="4"/>
@@ -184,7 +528,6 @@
               </c:pt>
             </c:numLit>
           </c:val>
-          <c:explosion val="15"/>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="bestFit"/>
@@ -248,11 +591,30 @@
           <c:tx>
             <c:v>Sales</c:v>
           </c:tx>
-          <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="2E75B6"/>
-            </a:solidFill>
-          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2E75B6"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
             <c:strLit>
               <c:ptCount val="3"/>
@@ -818,6 +1180,7 @@
               <a:lin ang="5400000" scaled="1"/>
             </a:gradFill>
           </c:spPr>
+          <c:explosion val="8"/>
           <c:cat>
             <c:strLit>
               <c:ptCount val="5"/>
@@ -859,7 +1222,6 @@
               </c:pt>
             </c:numLit>
           </c:val>
-          <c:explosion val="8"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -881,24 +1243,112 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>Pie — varyColors + firstSliceAngle</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Share</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Q1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Q2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Q3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Q4</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>20</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>10</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="45"/>
+      </c:pieChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Market Share"/>
+        <xdr:cNvPr id="2" name="Revenue by Region"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -907,7 +1357,37 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfb1a98cc16e64d60"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7207583305af47cc"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="3D Category Split"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc8cb5388a73d4963"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -917,18 +1397,18 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Revenue by Region"/>
+        <xdr:cNvPr id="4" name="Q4 Distribution"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -937,67 +1417,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02ed3eb5614b45fb"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="3D Category Split"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
-        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f9f91b207d04aee"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Q4 Distribution"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
-        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref73117fd6f44a96"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf4c2fecfdf084172"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1032,7 +1452,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8368f4da4e14bf7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref222689d5444f27"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1062,7 +1482,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R18f8e0f5c7af4c65"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc62460e65331490e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1092,7 +1512,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbec32a2d6d8a4428"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69e8619a4c7148ae"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1122,7 +1542,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R469388218b114605"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8c0d02e75e894055"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1131,16 +1551,148 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Pie — varyColors + firstSliceAngle"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50ccb9aab9f744aa"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Doughnut — holeSize + leaderlines"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R918ed831b8724591"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Overlaid Title"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24229d13de4b4c0b"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Doughnut — Combined"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd3e9ffdbb7a04d6f"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb3d1f11e6214a51"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f79aeaea42d416a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26b6bd1289ba44ae"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f51ea0d69d6441b"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfb018e9c3d34784"/>
 </x:worksheet>
 </file>